--- a/Apostas_Diarias/Apostas_20260417.xlsx
+++ b/Apostas_Diarias/Apostas_20260417.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="11_2B590F4F95664E55B160C5F050A3E834554BED1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFBC046D-3203-4C1D-9556-7429198EC5DF}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_2B590F4F95C6CD741D83DAF0502B00717091F834" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2591EA1-297B-4B4D-AE85-6D87CF645B6A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>Data</t>
   </si>
@@ -74,36 +74,18 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
-    <t>CHINA 1</t>
-  </si>
-  <si>
-    <t>Wuhan Three Towns x Chengdu Rongcheng</t>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>ITALY 1</t>
+  </si>
+  <si>
+    <t>Sassuolo x Como</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>11:30:00</t>
-  </si>
-  <si>
-    <t>ROMANIA 1</t>
-  </si>
-  <si>
-    <t>Otelul Galati x UTA Arad</t>
-  </si>
-  <si>
-    <t>14:00:00</t>
-  </si>
-  <si>
-    <t>NORWAY 2</t>
-  </si>
-  <si>
-    <t>Ranheim IL x Raufoss</t>
-  </si>
-  <si>
     <t>15:00:00</t>
   </si>
   <si>
@@ -116,12 +98,6 @@
     <t>Jong PSV Eindhoven x Jong Ajax Amsterdam</t>
   </si>
   <si>
-    <t>FRANCE 2</t>
-  </si>
-  <si>
-    <t>Pau x Guingamp</t>
-  </si>
-  <si>
     <t>Vitesse Arnhem x MVV Maastricht</t>
   </si>
   <si>
@@ -132,24 +108,6 @@
   </si>
   <si>
     <t>St Pauli x FC Koln</t>
-  </si>
-  <si>
-    <t>15:45:00</t>
-  </si>
-  <si>
-    <t>IRELAND 2</t>
-  </si>
-  <si>
-    <t>Kerry FC x Treaty United</t>
-  </si>
-  <si>
-    <t>UCD x Finn Harps</t>
-  </si>
-  <si>
-    <t>P4</t>
-  </si>
-  <si>
-    <t>Lay_CS_1x0_B365</t>
   </si>
 </sst>
 </file>
@@ -489,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -548,22 +506,22 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="H2">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
         <v>500</v>
@@ -574,7 +532,7 @@
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>33.392857142857146</v>
+        <v>54.360465116279073</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -588,36 +546,36 @@
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
         <v>16</v>
       </c>
       <c r="G3">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="I3">
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J17" si="0">IF(L3=1,"GREEN","RED")</f>
-        <v>RED</v>
+        <f t="shared" ref="J3:J6" si="0">IF(L3=1,"GREEN","RED")</f>
+        <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K17" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>-500</v>
+        <f t="shared" ref="K3:K6" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>33.392857142857146</v>
       </c>
       <c r="L3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -628,36 +586,36 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="H4">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="I4">
         <v>500</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="0"/>
-        <v>GREEN</v>
+        <v>RED</v>
       </c>
       <c r="K4">
         <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
+        <v>-500</v>
       </c>
       <c r="L4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -665,25 +623,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>9.8000000000000007</v>
+        <v>44</v>
       </c>
       <c r="H5">
-        <v>9.8000000000000007</v>
+        <v>44</v>
       </c>
       <c r="I5">
         <v>500</v>
@@ -694,7 +652,7 @@
       </c>
       <c r="K5">
         <f t="shared" si="1"/>
-        <v>53.125</v>
+        <v>10.872093023255815</v>
       </c>
       <c r="L5">
         <v>1</v>
@@ -708,22 +666,22 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F6" t="s">
         <v>16</v>
       </c>
       <c r="G6">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="H6">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="I6">
         <v>500</v>
@@ -734,456 +692,13 @@
       </c>
       <c r="K6">
         <f t="shared" si="1"/>
-        <v>40.652173913043484</v>
+        <v>49.210526315789473</v>
       </c>
       <c r="L6">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G7">
-        <v>10.5</v>
-      </c>
-      <c r="H7">
-        <v>10.5</v>
-      </c>
-      <c r="I7">
-        <v>500</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>12</v>
-      </c>
-      <c r="H8">
-        <v>12</v>
-      </c>
-      <c r="I8">
-        <v>500</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9">
-        <v>14.5</v>
-      </c>
-      <c r="H9">
-        <v>14.5</v>
-      </c>
-      <c r="I9">
-        <v>500</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="1"/>
-        <v>34.629629629629626</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10">
-        <v>29</v>
-      </c>
-      <c r="H10">
-        <v>29</v>
-      </c>
-      <c r="I10">
-        <v>500</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="1"/>
-        <v>16.696428571428573</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11">
-        <v>18.5</v>
-      </c>
-      <c r="H11">
-        <v>18.5</v>
-      </c>
-      <c r="I11">
-        <v>500</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="1"/>
-        <v>26.714285714285715</v>
-      </c>
-      <c r="L11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>10.5</v>
-      </c>
-      <c r="H12">
-        <v>10.5</v>
-      </c>
-      <c r="I12">
-        <v>500</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13">
-        <v>11.5</v>
-      </c>
-      <c r="H13">
-        <v>11.5</v>
-      </c>
-      <c r="I13">
-        <v>500</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K13">
-        <f t="shared" si="1"/>
-        <v>44.523809523809526</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" t="s">
-        <v>34</v>
-      </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>18</v>
-      </c>
-      <c r="H14">
-        <v>18</v>
-      </c>
-      <c r="I14">
-        <v>500</v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K14">
-        <f t="shared" si="1"/>
-        <v>27.5</v>
-      </c>
-      <c r="L14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" t="s">
-        <v>38</v>
-      </c>
-      <c r="G15">
-        <v>12</v>
-      </c>
-      <c r="H15">
-        <v>12</v>
-      </c>
-      <c r="I15">
-        <v>500</v>
-      </c>
-      <c r="J15" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K15">
-        <f t="shared" si="1"/>
-        <v>42.5</v>
-      </c>
-      <c r="L15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
-        <v>44</v>
-      </c>
-      <c r="H16">
-        <v>44</v>
-      </c>
-      <c r="I16">
-        <v>500</v>
-      </c>
-      <c r="J16" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K16">
-        <f t="shared" si="1"/>
-        <v>10.872093023255815</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="s">
-        <v>14</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>16</v>
-      </c>
-      <c r="G17">
-        <v>10.5</v>
-      </c>
-      <c r="H17">
-        <v>10.5</v>
-      </c>
-      <c r="I17">
-        <v>500</v>
-      </c>
-      <c r="J17" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
-      </c>
-      <c r="K17">
-        <f t="shared" si="1"/>
-        <v>-500</v>
-      </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
-    <sortCondition ref="E2:E17"/>
-  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Apostas_Diarias/Apostas_20260417.xlsx
+++ b/Apostas_Diarias/Apostas_20260417.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_2B590F4F95C6CD741D83DAF0502B00717091F834" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2591EA1-297B-4B4D-AE85-6D87CF645B6A}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_2B590F4F95B64F102960D9F050E438F26B5BF40B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{183405BC-97A5-498E-9D69-6807C80CC91B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>Data</t>
   </si>
@@ -74,6 +74,18 @@
     <t>P1 ⭐</t>
   </si>
   <si>
+    <t>09:00:00</t>
+  </si>
+  <si>
+    <t>CHINA 1</t>
+  </si>
+  <si>
+    <t>Wuhan Three Towns x Chengdu Rongcheng</t>
+  </si>
+  <si>
+    <t>Lay_CS_0x1_B365</t>
+  </si>
+  <si>
     <t>13:30:00</t>
   </si>
   <si>
@@ -81,24 +93,6 @@
   </si>
   <si>
     <t>Sassuolo x Como</t>
-  </si>
-  <si>
-    <t>Lay_CS_0x1_B365</t>
-  </si>
-  <si>
-    <t>15:00:00</t>
-  </si>
-  <si>
-    <t>NETHERLANDS 2</t>
-  </si>
-  <si>
-    <t>Helmond Sport x VVV Venlo</t>
-  </si>
-  <si>
-    <t>Jong PSV Eindhoven x Jong Ajax Amsterdam</t>
-  </si>
-  <si>
-    <t>Vitesse Arnhem x MVV Maastricht</t>
   </si>
   <si>
     <t>15:30:00</t>
@@ -447,13 +441,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -497,6 +491,9 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
+      <c r="L1">
+        <v>500</v>
+      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -518,24 +515,26 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <f>G2</f>
+        <v>10.5</v>
       </c>
       <c r="I2">
+        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
         <f>IF(L2=1,"GREEN","RED")</f>
-        <v>GREEN</v>
+        <v>RED</v>
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>54.360465116279073</v>
+        <v>-500</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -558,21 +557,23 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>9.6</v>
       </c>
       <c r="H3">
-        <v>15</v>
+        <f t="shared" ref="H3:H4" si="0">G3</f>
+        <v>9.6</v>
       </c>
       <c r="I3">
+        <f t="shared" ref="I3:I4" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J6" si="0">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K6" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>33.392857142857146</v>
+        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>54.360465116279073</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -586,115 +587,37 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
-        <v>85</v>
+        <v>10.5</v>
       </c>
       <c r="H4">
-        <v>85</v>
+        <f t="shared" si="0"/>
+        <v>10.5</v>
       </c>
       <c r="I4">
+        <f t="shared" si="1"/>
         <v>500</v>
       </c>
       <c r="J4" t="str">
-        <f t="shared" si="0"/>
-        <v>RED</v>
+        <f t="shared" si="2"/>
+        <v>GREEN</v>
       </c>
       <c r="K4">
-        <f t="shared" si="1"/>
-        <v>-500</v>
+        <f t="shared" si="3"/>
+        <v>49.210526315789473</v>
       </c>
       <c r="L4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5">
-        <v>44</v>
-      </c>
-      <c r="H5">
-        <v>44</v>
-      </c>
-      <c r="I5">
-        <v>500</v>
-      </c>
-      <c r="J5" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="1"/>
-        <v>10.872093023255815</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>10.5</v>
-      </c>
-      <c r="H6">
-        <v>10.5</v>
-      </c>
-      <c r="I6">
-        <v>500</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" si="0"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="1"/>
-        <v>49.210526315789473</v>
-      </c>
-      <c r="L6">
         <v>1</v>
       </c>
     </row>

--- a/Apostas_Diarias/Apostas_20260417.xlsx
+++ b/Apostas_Diarias/Apostas_20260417.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/Apostas_Diarias/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_2B590F4F95B64F102960D9F050E438F26B5BF40B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{183405BC-97A5-498E-9D69-6807C80CC91B}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_2B590F4F95C6CD741D83DAF0502B00717091F834" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2591EA1-297B-4B4D-AE85-6D87CF645B6A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="25">
   <si>
     <t>Data</t>
   </si>
@@ -74,25 +74,31 @@
     <t>P1 ⭐</t>
   </si>
   <si>
-    <t>09:00:00</t>
-  </si>
-  <si>
-    <t>CHINA 1</t>
-  </si>
-  <si>
-    <t>Wuhan Three Towns x Chengdu Rongcheng</t>
+    <t>13:30:00</t>
+  </si>
+  <si>
+    <t>ITALY 1</t>
+  </si>
+  <si>
+    <t>Sassuolo x Como</t>
   </si>
   <si>
     <t>Lay_CS_0x1_B365</t>
   </si>
   <si>
-    <t>13:30:00</t>
-  </si>
-  <si>
-    <t>ITALY 1</t>
-  </si>
-  <si>
-    <t>Sassuolo x Como</t>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>NETHERLANDS 2</t>
+  </si>
+  <si>
+    <t>Helmond Sport x VVV Venlo</t>
+  </si>
+  <si>
+    <t>Jong PSV Eindhoven x Jong Ajax Amsterdam</t>
+  </si>
+  <si>
+    <t>Vitesse Arnhem x MVV Maastricht</t>
   </si>
   <si>
     <t>15:30:00</t>
@@ -441,13 +447,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
@@ -491,9 +497,6 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1">
-        <v>500</v>
-      </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
@@ -515,26 +518,24 @@
         <v>16</v>
       </c>
       <c r="G2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="H2">
-        <f>G2</f>
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="I2">
-        <f>$L$1</f>
         <v>500</v>
       </c>
       <c r="J2" t="str">
         <f>IF(L2=1,"GREEN","RED")</f>
-        <v>RED</v>
+        <v>GREEN</v>
       </c>
       <c r="K2">
         <f>IF(L2=1,0.935/(H2-1)*I2,-500)</f>
-        <v>-500</v>
+        <v>54.360465116279073</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -557,23 +558,21 @@
         <v>16</v>
       </c>
       <c r="G3">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="H3">
-        <f t="shared" ref="H3:H4" si="0">G3</f>
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I4" si="1">$L$1</f>
         <v>500</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J4" si="2">IF(L3=1,"GREEN","RED")</f>
+        <f t="shared" ref="J3:J6" si="0">IF(L3=1,"GREEN","RED")</f>
         <v>GREEN</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K4" si="3">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
-        <v>54.360465116279073</v>
+        <f t="shared" ref="K3:K6" si="1">IF(L3=1,0.935/(H3-1)*I3,-500)</f>
+        <v>33.392857142857146</v>
       </c>
       <c r="L3">
         <v>1</v>
@@ -587,37 +586,115 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
-      </c>
-      <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
       </c>
       <c r="F4" t="s">
         <v>16</v>
       </c>
       <c r="G4">
+        <v>85</v>
+      </c>
+      <c r="H4">
+        <v>85</v>
+      </c>
+      <c r="I4">
+        <v>500</v>
+      </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="1"/>
+        <v>-500</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>44</v>
+      </c>
+      <c r="H5">
+        <v>44</v>
+      </c>
+      <c r="I5">
+        <v>500</v>
+      </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="1"/>
+        <v>10.872093023255815</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
         <v>10.5</v>
       </c>
-      <c r="H4">
+      <c r="H6">
+        <v>10.5</v>
+      </c>
+      <c r="I6">
+        <v>500</v>
+      </c>
+      <c r="J6" t="str">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="I4">
+        <v>GREEN</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="1"/>
-        <v>500</v>
-      </c>
-      <c r="J4" t="str">
-        <f t="shared" si="2"/>
-        <v>GREEN</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="3"/>
         <v>49.210526315789473</v>
       </c>
-      <c r="L4">
+      <c r="L6">
         <v>1</v>
       </c>
     </row>
